--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run8/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run8/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -811,769 +811,778 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9586,0.0081,0.0137,0.0089</t>
-  </si>
-  <si>
-    <t>0.0065,0.0213,0.0004,0.9952</t>
-  </si>
-  <si>
-    <t>0.9479,0.0003,0.0002,0.1170</t>
-  </si>
-  <si>
-    <t>0.5965,0.0002,0.0024,0.5360</t>
-  </si>
-  <si>
-    <t>0.9950,0.0006,0.0007,0.0019</t>
-  </si>
-  <si>
-    <t>0.9918,0.0035,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9960,0.0011,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9974,0.0011,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9938,0.0021,0.0005,0.0021</t>
-  </si>
-  <si>
-    <t>0.9945,0.0018,0.0008,0.0012</t>
-  </si>
-  <si>
-    <t>0.9961,0.0012,0.0008,0.0011</t>
-  </si>
-  <si>
-    <t>0.9962,0.0010,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.8892,0.0382,0.0441,0.0061</t>
-  </si>
-  <si>
-    <t>0.2072,0.0193,0.8141,0.0025</t>
-  </si>
-  <si>
-    <t>0.6284,0.0023,0.6448,0.0002</t>
-  </si>
-  <si>
-    <t>0.0095,0.0045,0.9889,0.0005</t>
-  </si>
-  <si>
-    <t>0.8216,0.0080,0.2240,0.0025</t>
-  </si>
-  <si>
-    <t>0.0006,0.9987,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.2592,0.8337,0.0043,0.0014</t>
-  </si>
-  <si>
-    <t>0.0061,0.9887,0.0027,0.0012</t>
-  </si>
-  <si>
-    <t>0.0007,0.9980,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.1420,0.0072,0.9030,0.0029</t>
-  </si>
-  <si>
-    <t>0.7133,0.0057,0.3154,0.0129</t>
-  </si>
-  <si>
-    <t>0.0187,0.0010,0.9855,0.0009</t>
-  </si>
-  <si>
-    <t>0.0012,0.0002,0.9949,0.0040</t>
-  </si>
-  <si>
-    <t>0.0464,0.0028,0.9668,0.0012</t>
-  </si>
-  <si>
-    <t>0.0387,0.0008,0.9658,0.0026</t>
-  </si>
-  <si>
-    <t>0.0058,0.0015,0.9887,0.0040</t>
-  </si>
-  <si>
-    <t>0.8568,0.1693,0.0102,0.0007</t>
-  </si>
-  <si>
-    <t>0.6475,0.1357,0.1229,0.0016</t>
-  </si>
-  <si>
-    <t>0.0082,0.0482,0.9786,0.0097</t>
-  </si>
-  <si>
-    <t>0.0122,0.9723,0.0357,0.0009</t>
-  </si>
-  <si>
-    <t>0.9866,0.0098,0.0020,0.0006</t>
-  </si>
-  <si>
-    <t>0.9860,0.0090,0.0016,0.0010</t>
-  </si>
-  <si>
-    <t>0.9123,0.1633,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.0043,0.9881,0.3398,0.0013</t>
-  </si>
-  <si>
-    <t>0.0392,0.4414,0.3394,0.0234</t>
-  </si>
-  <si>
-    <t>0.0526,0.0401,0.9236,0.0152</t>
-  </si>
-  <si>
-    <t>0.0418,0.0193,0.9625,0.0025</t>
-  </si>
-  <si>
-    <t>0.0178,0.0024,0.9735,0.0056</t>
-  </si>
-  <si>
-    <t>0.0402,0.0358,0.9699,0.0012</t>
-  </si>
-  <si>
-    <t>0.0062,0.9646,0.0602,0.0020</t>
-  </si>
-  <si>
-    <t>0.0061,0.0174,0.9932,0.0002</t>
-  </si>
-  <si>
-    <t>0.0155,0.7597,0.0109,0.7228</t>
-  </si>
-  <si>
-    <t>0.0010,0.9905,0.0023,0.0016</t>
-  </si>
-  <si>
-    <t>0.0007,0.9962,0.0028,0.0006</t>
-  </si>
-  <si>
-    <t>0.0005,0.9961,0.0028,0.0011</t>
-  </si>
-  <si>
-    <t>0.0026,0.0792,0.9793,0.0118</t>
-  </si>
-  <si>
-    <t>0.0027,0.0756,0.9945,0.0002</t>
-  </si>
-  <si>
-    <t>0.0015,0.0013,0.9936,0.0063</t>
-  </si>
-  <si>
-    <t>0.0113,0.0017,0.9764,0.0122</t>
-  </si>
-  <si>
-    <t>0.0061,0.0040,0.9903,0.0007</t>
-  </si>
-  <si>
-    <t>0.0070,0.0044,0.9877,0.0010</t>
-  </si>
-  <si>
-    <t>0.9493,0.0552,0.0095,0.0022</t>
-  </si>
-  <si>
-    <t>0.9898,0.0008,0.0065,0.0009</t>
-  </si>
-  <si>
-    <t>0.9804,0.0124,0.0026,0.0021</t>
-  </si>
-  <si>
-    <t>0.0088,0.0372,0.9885,0.0024</t>
-  </si>
-  <si>
-    <t>0.9592,0.0147,0.0166,0.0082</t>
-  </si>
-  <si>
-    <t>0.9881,0.0059,0.0028,0.0016</t>
-  </si>
-  <si>
-    <t>0.9948,0.0030,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.0028,0.8180,0.9759,0.0007</t>
-  </si>
-  <si>
-    <t>0.0092,0.0510,0.9551,0.0071</t>
-  </si>
-  <si>
-    <t>0.0329,0.0823,0.9453,0.0049</t>
-  </si>
-  <si>
-    <t>0.0008,0.9752,0.9595,0.0007</t>
-  </si>
-  <si>
-    <t>0.0006,0.0046,0.9962,0.0040</t>
-  </si>
-  <si>
-    <t>0.0201,0.9719,0.0155,0.0009</t>
-  </si>
-  <si>
-    <t>0.0088,0.9882,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.8367,0.0220,0.2293,0.0045</t>
-  </si>
-  <si>
-    <t>0.9569,0.0195,0.0254,0.0011</t>
-  </si>
-  <si>
-    <t>0.0032,0.0037,0.9912,0.0041</t>
-  </si>
-  <si>
-    <t>0.0014,0.8455,0.9853,0.0004</t>
-  </si>
-  <si>
-    <t>0.0024,0.9716,0.5226,0.0007</t>
-  </si>
-  <si>
-    <t>0.0026,0.9938,0.0623,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.9856,0.5339,0.0004</t>
-  </si>
-  <si>
-    <t>0.0039,0.0007,0.0070,0.9937</t>
-  </si>
-  <si>
-    <t>0.0014,0.0007,0.0009,0.9984</t>
-  </si>
-  <si>
-    <t>0.0071,0.0034,0.0007,0.9961</t>
-  </si>
-  <si>
-    <t>0.0091,0.0094,0.0072,0.9872</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.0009,0.9991</t>
-  </si>
-  <si>
-    <t>0.0219,0.0008,0.0006,0.9920</t>
-  </si>
-  <si>
-    <t>0.0027,0.9641,0.8833,0.0021</t>
-  </si>
-  <si>
-    <t>0.0002,0.9620,0.9952,0.0001</t>
-  </si>
-  <si>
-    <t>0.0151,0.9437,0.1714,0.0018</t>
-  </si>
-  <si>
-    <t>0.0038,0.7513,0.8805,0.0061</t>
-  </si>
-  <si>
-    <t>0.0007,0.9912,0.8150,0.0002</t>
-  </si>
-  <si>
-    <t>0.0083,0.7577,0.7673,0.0022</t>
-  </si>
-  <si>
-    <t>0.9976,0.0016,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9039,0.1215,0.0115,0.0016</t>
-  </si>
-  <si>
-    <t>0.9161,0.1168,0.0081,0.0014</t>
-  </si>
-  <si>
-    <t>0.9860,0.0146,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9938,0.0049,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9971,0.0011,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9737,0.0205,0.0085,0.0023</t>
-  </si>
-  <si>
-    <t>0.9911,0.0072,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0000,0.0010</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9962,0.0017,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9986,0.0002,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9973,0.0012,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9973,0.0005,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0226,0.0007,0.9823,0.0004</t>
-  </si>
-  <si>
-    <t>0.0144,0.0064,0.9882,0.0004</t>
-  </si>
-  <si>
-    <t>0.9389,0.0044,0.0407,0.0086</t>
-  </si>
-  <si>
-    <t>0.0093,0.0014,0.9826,0.0060</t>
-  </si>
-  <si>
-    <t>0.0042,0.9930,0.0018,0.0014</t>
-  </si>
-  <si>
-    <t>0.0005,0.9991,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.0166,0.9739,0.0063,0.0047</t>
-  </si>
-  <si>
-    <t>0.0148,0.9663,0.0135,0.0021</t>
-  </si>
-  <si>
-    <t>0.0014,0.9974,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0030,0.9940,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.6318,0.3915,0.0087,0.0026</t>
-  </si>
-  <si>
-    <t>0.9660,0.0168,0.0094,0.0014</t>
-  </si>
-  <si>
-    <t>0.2031,0.0044,0.8194,0.0085</t>
-  </si>
-  <si>
-    <t>0.5888,0.2381,0.1418,0.0194</t>
-  </si>
-  <si>
-    <t>0.3212,0.0195,0.7536,0.0110</t>
-  </si>
-  <si>
-    <t>0.0149,0.0263,0.0241,0.9765</t>
-  </si>
-  <si>
-    <t>0.0015,0.9956,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.0026,0.9948,0.0233,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.9980,0.0007,0.0059</t>
-  </si>
-  <si>
-    <t>0.0008,0.9633,0.9425,0.0004</t>
-  </si>
-  <si>
-    <t>0.0041,0.9932,0.0021,0.0004</t>
-  </si>
-  <si>
-    <t>0.9852,0.0257,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.7233,0.3967,0.0021,0.0005</t>
-  </si>
-  <si>
-    <t>0.9986,0.0005,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9962,0.0016,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9968,0.0008,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9942,0.0007,0.0002,0.0028</t>
-  </si>
-  <si>
-    <t>0.9946,0.0023,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.9945,0.0007,0.0002,0.0032</t>
-  </si>
-  <si>
-    <t>0.9961,0.0013,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.0051,0.9776,0.3944,0.0005</t>
-  </si>
-  <si>
-    <t>0.0083,0.7708,0.9220,0.0018</t>
-  </si>
-  <si>
-    <t>0.0728,0.0098,0.9530,0.0004</t>
-  </si>
-  <si>
-    <t>0.0405,0.1240,0.9404,0.0030</t>
-  </si>
-  <si>
-    <t>0.9946,0.0005,0.0025,0.0004</t>
-  </si>
-  <si>
-    <t>0.8819,0.0013,0.2660,0.0009</t>
-  </si>
-  <si>
-    <t>0.4244,0.0048,0.7137,0.0052</t>
-  </si>
-  <si>
-    <t>0.9222,0.0039,0.0692,0.0035</t>
-  </si>
-  <si>
-    <t>0.2278,0.0011,0.0014,0.8948</t>
-  </si>
-  <si>
-    <t>0.0003,0.0005,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0009,0.0766,0.0010,0.9971</t>
-  </si>
-  <si>
-    <t>0.0019,0.0001,0.0004,0.9986</t>
-  </si>
-  <si>
-    <t>0.0022,0.9557,0.6654,0.0040</t>
-  </si>
-  <si>
-    <t>0.9851,0.0135,0.0009,0.0010</t>
-  </si>
-  <si>
-    <t>0.0472,0.9441,0.0150,0.0232</t>
-  </si>
-  <si>
-    <t>0.9916,0.0011,0.0024,0.0028</t>
-  </si>
-  <si>
-    <t>0.3083,0.7762,0.0066,0.0012</t>
-  </si>
-  <si>
-    <t>0.9896,0.0007,0.0009,0.0078</t>
-  </si>
-  <si>
-    <t>0.5713,0.0022,0.0022,0.6939</t>
-  </si>
-  <si>
-    <t>0.9920,0.0019,0.0007,0.0021</t>
-  </si>
-  <si>
-    <t>0.0002,0.0008,0.9873,0.2323</t>
-  </si>
-  <si>
-    <t>0.9659,0.0004,0.0011,0.0368</t>
-  </si>
-  <si>
-    <t>0.9095,0.0032,0.0045,0.0726</t>
-  </si>
-  <si>
-    <t>0.8338,0.2326,0.0083,0.0024</t>
-  </si>
-  <si>
-    <t>0.9832,0.0048,0.0069,0.0009</t>
-  </si>
-  <si>
-    <t>0.9690,0.0262,0.0062,0.0006</t>
-  </si>
-  <si>
-    <t>0.1598,0.2666,0.5938,0.0178</t>
-  </si>
-  <si>
-    <t>0.9476,0.0366,0.0179,0.0012</t>
-  </si>
-  <si>
-    <t>0.9735,0.0147,0.0098,0.0008</t>
-  </si>
-  <si>
-    <t>0.9947,0.0008,0.0011,0.0020</t>
-  </si>
-  <si>
-    <t>0.9949,0.0011,0.0003,0.0018</t>
-  </si>
-  <si>
-    <t>0.9915,0.0037,0.0016,0.0011</t>
-  </si>
-  <si>
-    <t>0.9894,0.0027,0.0021,0.0032</t>
-  </si>
-  <si>
-    <t>0.9904,0.0054,0.0013,0.0015</t>
-  </si>
-  <si>
-    <t>0.9640,0.0275,0.0047,0.0035</t>
-  </si>
-  <si>
-    <t>0.9983,0.0001,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9929,0.0005,0.0006,0.0048</t>
-  </si>
-  <si>
-    <t>0.8860,0.0506,0.0010,0.0137</t>
-  </si>
-  <si>
-    <t>0.8107,0.2242,0.0098,0.0038</t>
-  </si>
-  <si>
-    <t>0.9175,0.1077,0.0058,0.0011</t>
-  </si>
-  <si>
-    <t>0.8116,0.1643,0.0330,0.0144</t>
-  </si>
-  <si>
-    <t>0.7527,0.2934,0.0078,0.0034</t>
-  </si>
-  <si>
-    <t>0.9955,0.0011,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.9882,0.0026,0.0062,0.0014</t>
-  </si>
-  <si>
-    <t>0.9433,0.0697,0.0027,0.0014</t>
-  </si>
-  <si>
-    <t>0.0038,0.0675,0.9948,0.0006</t>
-  </si>
-  <si>
-    <t>0.9691,0.0252,0.0045,0.0016</t>
-  </si>
-  <si>
-    <t>0.0094,0.0014,0.9922,0.0004</t>
-  </si>
-  <si>
-    <t>0.0103,0.2151,0.9675,0.0142</t>
-  </si>
-  <si>
-    <t>0.0143,0.0040,0.9803,0.0063</t>
-  </si>
-  <si>
-    <t>0.0087,0.0140,0.9821,0.0025</t>
-  </si>
-  <si>
-    <t>0.0185,0.0156,0.9863,0.0005</t>
-  </si>
-  <si>
-    <t>0.0088,0.0002,0.9936,0.0002</t>
-  </si>
-  <si>
-    <t>0.0021,0.0074,0.9955,0.0010</t>
-  </si>
-  <si>
-    <t>0.3570,0.0050,0.7117,0.0105</t>
-  </si>
-  <si>
-    <t>0.2953,0.0017,0.8457,0.0008</t>
-  </si>
-  <si>
-    <t>0.1128,0.0646,0.8246,0.0115</t>
-  </si>
-  <si>
-    <t>0.1844,0.0716,0.7662,0.0087</t>
-  </si>
-  <si>
-    <t>0.2145,0.0627,0.6666,0.0029</t>
-  </si>
-  <si>
-    <t>0.1136,0.5091,0.2522,0.0226</t>
-  </si>
-  <si>
-    <t>0.7893,0.0702,0.0989,0.0095</t>
-  </si>
-  <si>
-    <t>0.3605,0.0225,0.6804,0.0104</t>
-  </si>
-  <si>
-    <t>0.0113,0.9858,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.0302,0.9702,0.0063,0.0014</t>
-  </si>
-  <si>
-    <t>0.0588,0.9733,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.8146,0.2421,0.0111,0.0051</t>
-  </si>
-  <si>
-    <t>0.4871,0.6677,0.0018,0.0014</t>
-  </si>
-  <si>
-    <t>0.9604,0.0275,0.0067,0.0001</t>
-  </si>
-  <si>
-    <t>0.9673,0.0010,0.0463,0.0014</t>
-  </si>
-  <si>
-    <t>0.9151,0.0018,0.0140,0.0466</t>
-  </si>
-  <si>
-    <t>0.8174,0.0011,0.3132,0.0007</t>
-  </si>
-  <si>
-    <t>0.3474,0.0018,0.7260,0.0034</t>
-  </si>
-  <si>
-    <t>0.0099,0.0058,0.9803,0.0066</t>
-  </si>
-  <si>
-    <t>0.0366,0.0339,0.9161,0.0403</t>
-  </si>
-  <si>
-    <t>0.0247,0.0195,0.9699,0.0016</t>
-  </si>
-  <si>
-    <t>0.1983,0.0041,0.8905,0.0021</t>
-  </si>
-  <si>
-    <t>0.0022,0.0392,0.9919,0.0019</t>
-  </si>
-  <si>
-    <t>0.9971,0.0005,0.0000,0.0011</t>
-  </si>
-  <si>
-    <t>0.9929,0.0024,0.0025,0.0008</t>
-  </si>
-  <si>
-    <t>0.9434,0.0585,0.0032,0.0030</t>
-  </si>
-  <si>
-    <t>0.9878,0.0142,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9801,0.0183,0.0009,0.0015</t>
-  </si>
-  <si>
-    <t>0.9908,0.0051,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.9944,0.0035,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9984,0.0001,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.0091,0.0897,0.9716,0.0091</t>
-  </si>
-  <si>
-    <t>0.1260,0.1196,0.8132,0.0252</t>
-  </si>
-  <si>
-    <t>0.9544,0.0019,0.0428,0.0019</t>
-  </si>
-  <si>
-    <t>0.0187,0.0037,0.9858,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0023,0.9945,0.0091</t>
-  </si>
-  <si>
-    <t>0.0015,0.0610,0.9816,0.0126</t>
-  </si>
-  <si>
-    <t>0.0027,0.0010,0.9944,0.0005</t>
-  </si>
-  <si>
-    <t>0.1245,0.0513,0.7959,0.0043</t>
-  </si>
-  <si>
-    <t>0.0002,0.0072,0.9973,0.0033</t>
-  </si>
-  <si>
-    <t>0.0041,0.0023,0.9869,0.0074</t>
-  </si>
-  <si>
-    <t>0.0448,0.0197,0.9375,0.0069</t>
-  </si>
-  <si>
-    <t>0.9444,0.0030,0.0509,0.0055</t>
-  </si>
-  <si>
-    <t>0.8865,0.0046,0.1313,0.0060</t>
-  </si>
-  <si>
-    <t>0.9509,0.0034,0.0637,0.0012</t>
-  </si>
-  <si>
-    <t>0.9946,0.0016,0.0014,0.0010</t>
-  </si>
-  <si>
-    <t>0.9915,0.0092,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9985,0.0009,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9869,0.0125,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9969,0.0006,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9890,0.0118,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.9909,0.0041,0.0028,0.0009</t>
-  </si>
-  <si>
-    <t>0.9931,0.0039,0.0010,0.0007</t>
-  </si>
-  <si>
-    <t>0.0433,0.0189,0.9157,0.0159</t>
-  </si>
-  <si>
-    <t>0.0064,0.0431,0.9904,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.0364,0.9943,0.0030</t>
-  </si>
-  <si>
-    <t>0.0046,0.0158,0.9856,0.0029</t>
-  </si>
-  <si>
-    <t>0.0038,0.0056,0.9854,0.0055</t>
-  </si>
-  <si>
-    <t>0.2772,0.0016,0.2919,0.1669</t>
-  </si>
-  <si>
-    <t>0.1450,0.0045,0.8886,0.0048</t>
-  </si>
-  <si>
-    <t>0.0463,0.0039,0.9572,0.0047</t>
-  </si>
-  <si>
-    <t>0.9924,0.0002,0.0013,0.0036</t>
-  </si>
-  <si>
-    <t>0.0618,0.0129,0.0077,0.9671</t>
-  </si>
-  <si>
-    <t>0.0865,0.0015,0.0032,0.9621</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0026,0.9993</t>
-  </si>
-  <si>
-    <t>0.0009,0.0003,0.0010,0.9987</t>
-  </si>
-  <si>
-    <t>0.9722,0.0012,0.0044,0.0173</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9841,0.0019,0.0059,0.0028</t>
+  </si>
+  <si>
+    <t>0.0068,0.0019,0.0005,0.9964</t>
+  </si>
+  <si>
+    <t>0.9548,0.0044,0.0007,0.0296</t>
+  </si>
+  <si>
+    <t>0.0330,0.0003,0.0015,0.9866</t>
+  </si>
+  <si>
+    <t>0.9967,0.0007,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9965,0.0013,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9981,0.0009,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9968,0.0015,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9933,0.0022,0.0011,0.0015</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9961,0.0013,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9358,0.0364,0.0129,0.0022</t>
+  </si>
+  <si>
+    <t>0.4645,0.0043,0.7018,0.0008</t>
+  </si>
+  <si>
+    <t>0.7876,0.0026,0.3540,0.0012</t>
+  </si>
+  <si>
+    <t>0.0221,0.0027,0.9815,0.0011</t>
+  </si>
+  <si>
+    <t>0.9643,0.0036,0.0326,0.0009</t>
+  </si>
+  <si>
+    <t>0.0020,0.9961,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9987,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.0242,0.9793,0.0038,0.0004</t>
+  </si>
+  <si>
+    <t>0.0130,0.9782,0.0036,0.0016</t>
+  </si>
+  <si>
+    <t>0.0009,0.9980,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0953,0.0026,0.9015,0.0103</t>
+  </si>
+  <si>
+    <t>0.2844,0.0033,0.8164,0.0024</t>
+  </si>
+  <si>
+    <t>0.0163,0.0010,0.9802,0.0052</t>
+  </si>
+  <si>
+    <t>0.0447,0.0099,0.9532,0.0036</t>
+  </si>
+  <si>
+    <t>0.0855,0.0004,0.9595,0.0002</t>
+  </si>
+  <si>
+    <t>0.0429,0.0008,0.9533,0.0055</t>
+  </si>
+  <si>
+    <t>0.0035,0.0009,0.9922,0.0052</t>
+  </si>
+  <si>
+    <t>0.9386,0.0381,0.0203,0.0005</t>
+  </si>
+  <si>
+    <t>0.7372,0.1335,0.1153,0.0064</t>
+  </si>
+  <si>
+    <t>0.0113,0.0136,0.9800,0.0031</t>
+  </si>
+  <si>
+    <t>0.0645,0.7054,0.1941,0.0002</t>
+  </si>
+  <si>
+    <t>0.9090,0.1122,0.0065,0.0014</t>
+  </si>
+  <si>
+    <t>0.9580,0.0200,0.0249,0.0011</t>
+  </si>
+  <si>
+    <t>0.9274,0.0930,0.0024,0.0007</t>
+  </si>
+  <si>
+    <t>0.0108,0.9783,0.1241,0.0053</t>
+  </si>
+  <si>
+    <t>0.0323,0.1248,0.6981,0.0290</t>
+  </si>
+  <si>
+    <t>0.0573,0.0107,0.9627,0.0016</t>
+  </si>
+  <si>
+    <t>0.0126,0.0161,0.9803,0.0034</t>
+  </si>
+  <si>
+    <t>0.3648,0.0021,0.5503,0.0199</t>
+  </si>
+  <si>
+    <t>0.0126,0.1400,0.9838,0.0004</t>
+  </si>
+  <si>
+    <t>0.0053,0.9775,0.0230,0.0009</t>
+  </si>
+  <si>
+    <t>0.0105,0.2549,0.9678,0.0029</t>
+  </si>
+  <si>
+    <t>0.0411,0.5385,0.0105,0.7691</t>
+  </si>
+  <si>
+    <t>0.0010,0.9896,0.0008,0.0049</t>
+  </si>
+  <si>
+    <t>0.0007,0.9967,0.0044,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.9972,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.0021,0.0079,0.9899,0.0060</t>
+  </si>
+  <si>
+    <t>0.0049,0.3116,0.9802,0.0011</t>
+  </si>
+  <si>
+    <t>0.0043,0.0007,0.9927,0.0019</t>
+  </si>
+  <si>
+    <t>0.0013,0.0009,0.9945,0.0081</t>
+  </si>
+  <si>
+    <t>0.0022,0.0010,0.9960,0.0006</t>
+  </si>
+  <si>
+    <t>0.0203,0.0160,0.9733,0.0017</t>
+  </si>
+  <si>
+    <t>0.8875,0.1894,0.0042,0.0010</t>
+  </si>
+  <si>
+    <t>0.9947,0.0017,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.9241,0.0360,0.0221,0.0215</t>
+  </si>
+  <si>
+    <t>0.0042,0.0153,0.9902,0.0088</t>
+  </si>
+  <si>
+    <t>0.9811,0.0053,0.0068,0.0050</t>
+  </si>
+  <si>
+    <t>0.9943,0.0021,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.9944,0.0027,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.0033,0.8652,0.9520,0.0009</t>
+  </si>
+  <si>
+    <t>0.0166,0.2423,0.9123,0.0095</t>
+  </si>
+  <si>
+    <t>0.0093,0.0641,0.9742,0.0038</t>
+  </si>
+  <si>
+    <t>0.0019,0.8176,0.9832,0.0016</t>
+  </si>
+  <si>
+    <t>0.0005,0.0007,0.9961,0.0056</t>
+  </si>
+  <si>
+    <t>0.0080,0.9746,0.2249,0.0012</t>
+  </si>
+  <si>
+    <t>0.0071,0.9896,0.0056,0.0001</t>
+  </si>
+  <si>
+    <t>0.8966,0.0069,0.2266,0.0017</t>
+  </si>
+  <si>
+    <t>0.0346,0.1439,0.9415,0.0045</t>
+  </si>
+  <si>
+    <t>0.0054,0.0058,0.9923,0.0011</t>
+  </si>
+  <si>
+    <t>0.0010,0.8234,0.9891,0.0006</t>
+  </si>
+  <si>
+    <t>0.0169,0.9274,0.1944,0.0058</t>
+  </si>
+  <si>
+    <t>0.0011,0.9887,0.8057,0.0002</t>
+  </si>
+  <si>
+    <t>0.0040,0.9756,0.5094,0.0012</t>
+  </si>
+  <si>
+    <t>0.0019,0.0004,0.0219,0.9936</t>
+  </si>
+  <si>
+    <t>0.0044,0.0003,0.0003,0.9976</t>
+  </si>
+  <si>
+    <t>0.0035,0.0137,0.0001,0.9974</t>
+  </si>
+  <si>
+    <t>0.0121,0.0021,0.0032,0.9900</t>
+  </si>
+  <si>
+    <t>0.0056,0.0014,0.0013,0.9964</t>
+  </si>
+  <si>
+    <t>0.0055,0.0012,0.0002,0.9975</t>
+  </si>
+  <si>
+    <t>0.0027,0.9876,0.4553,0.0013</t>
+  </si>
+  <si>
+    <t>0.0001,0.9850,0.9935,0.0000</t>
+  </si>
+  <si>
+    <t>0.0299,0.9226,0.0912,0.0005</t>
+  </si>
+  <si>
+    <t>0.0063,0.9591,0.4000,0.0030</t>
+  </si>
+  <si>
+    <t>0.0005,0.9784,0.9791,0.0002</t>
+  </si>
+  <si>
+    <t>0.0040,0.1133,0.9755,0.0021</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9898,0.0056,0.0006,0.0015</t>
+  </si>
+  <si>
+    <t>0.9921,0.0051,0.0015,0.0009</t>
+  </si>
+  <si>
+    <t>0.9939,0.0033,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9971,0.0010,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9879,0.0089,0.0011,0.0012</t>
+  </si>
+  <si>
+    <t>0.9827,0.0104,0.0024,0.0019</t>
+  </si>
+  <si>
+    <t>0.9906,0.0097,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9980,0.0002,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0004,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9977,0.0007,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9963,0.0005,0.0014,0.0006</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.0203,0.0037,0.9832,0.0004</t>
+  </si>
+  <si>
+    <t>0.0297,0.0079,0.9772,0.0005</t>
+  </si>
+  <si>
+    <t>0.8746,0.0121,0.1187,0.0028</t>
+  </si>
+  <si>
+    <t>0.0270,0.0009,0.9754,0.0019</t>
+  </si>
+  <si>
+    <t>0.0022,0.9960,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.0007,0.9980,0.0029,0.0002</t>
+  </si>
+  <si>
+    <t>0.0155,0.9591,0.0233,0.0122</t>
+  </si>
+  <si>
+    <t>0.0214,0.9506,0.0260,0.0066</t>
+  </si>
+  <si>
+    <t>0.0048,0.9881,0.0040,0.0034</t>
+  </si>
+  <si>
+    <t>0.0012,0.9974,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.4856,0.5143,0.0171,0.0011</t>
+  </si>
+  <si>
+    <t>0.9604,0.0026,0.0402,0.0024</t>
+  </si>
+  <si>
+    <t>0.4393,0.0019,0.6833,0.0034</t>
+  </si>
+  <si>
+    <t>0.3114,0.2954,0.2078,0.0065</t>
+  </si>
+  <si>
+    <t>0.5713,0.0103,0.5753,0.0071</t>
+  </si>
+  <si>
+    <t>0.0112,0.0509,0.1298,0.9184</t>
+  </si>
+  <si>
+    <t>0.0010,0.9960,0.0039,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.9940,0.0077,0.0015</t>
+  </si>
+  <si>
+    <t>0.0009,0.9961,0.0017,0.0154</t>
+  </si>
+  <si>
+    <t>0.0012,0.9771,0.8810,0.0014</t>
+  </si>
+  <si>
+    <t>0.0083,0.9915,0.0098,0.0005</t>
+  </si>
+  <si>
+    <t>0.9749,0.0345,0.0022,0.0002</t>
+  </si>
+  <si>
+    <t>0.5476,0.5597,0.0023,0.0017</t>
+  </si>
+  <si>
+    <t>0.9979,0.0008,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9954,0.0016,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9960,0.0012,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9952,0.0009,0.0015,0.0010</t>
+  </si>
+  <si>
+    <t>0.9979,0.0005,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9949,0.0005,0.0017,0.0010</t>
+  </si>
+  <si>
+    <t>0.9924,0.0034,0.0014,0.0011</t>
+  </si>
+  <si>
+    <t>0.0010,0.9631,0.9721,0.0006</t>
+  </si>
+  <si>
+    <t>0.0090,0.5547,0.9367,0.0017</t>
+  </si>
+  <si>
+    <t>0.0945,0.0515,0.8976,0.0019</t>
+  </si>
+  <si>
+    <t>0.0268,0.0136,0.9668,0.0042</t>
+  </si>
+  <si>
+    <t>0.9896,0.0013,0.0056,0.0007</t>
+  </si>
+  <si>
+    <t>0.9704,0.0020,0.0376,0.0010</t>
+  </si>
+  <si>
+    <t>0.5603,0.0016,0.7325,0.0005</t>
+  </si>
+  <si>
+    <t>0.7185,0.0280,0.1559,0.0839</t>
+  </si>
+  <si>
+    <t>0.0819,0.0011,0.0075,0.9381</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0010,0.0028,0.0009,0.9985</t>
+  </si>
+  <si>
+    <t>0.0013,0.0004,0.0008,0.9987</t>
+  </si>
+  <si>
+    <t>0.0009,0.9514,0.9502,0.0007</t>
+  </si>
+  <si>
+    <t>0.9930,0.0047,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.0481,0.9472,0.0150,0.0040</t>
+  </si>
+  <si>
+    <t>0.9938,0.0012,0.0028,0.0007</t>
+  </si>
+  <si>
+    <t>0.0886,0.9243,0.0170,0.0017</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.8370,0.0038,0.0076,0.3022</t>
+  </si>
+  <si>
+    <t>0.9969,0.0008,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0025,0.0056,0.9821,0.0427</t>
+  </si>
+  <si>
+    <t>0.9606,0.0002,0.0016,0.0329</t>
+  </si>
+  <si>
+    <t>0.9768,0.0030,0.0026,0.0118</t>
+  </si>
+  <si>
+    <t>0.5684,0.4029,0.0633,0.0025</t>
+  </si>
+  <si>
+    <t>0.9448,0.0117,0.0156,0.0122</t>
+  </si>
+  <si>
+    <t>0.9896,0.0073,0.0018,0.0002</t>
+  </si>
+  <si>
+    <t>0.0336,0.9572,0.0064,0.0016</t>
+  </si>
+  <si>
+    <t>0.9553,0.0609,0.0033,0.0003</t>
+  </si>
+  <si>
+    <t>0.9466,0.0383,0.0115,0.0042</t>
+  </si>
+  <si>
+    <t>0.9925,0.0039,0.0012,0.0013</t>
+  </si>
+  <si>
+    <t>0.9979,0.0003,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9815,0.0086,0.0016,0.0060</t>
+  </si>
+  <si>
+    <t>0.9933,0.0011,0.0021,0.0012</t>
+  </si>
+  <si>
+    <t>0.9830,0.0064,0.0051,0.0027</t>
+  </si>
+  <si>
+    <t>0.9897,0.0063,0.0022,0.0006</t>
+  </si>
+  <si>
+    <t>0.9954,0.0002,0.0010,0.0017</t>
+  </si>
+  <si>
+    <t>0.9959,0.0007,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9507,0.0204,0.0004,0.0055</t>
+  </si>
+  <si>
+    <t>0.7200,0.3289,0.0275,0.0043</t>
+  </si>
+  <si>
+    <t>0.3953,0.7275,0.0045,0.0009</t>
+  </si>
+  <si>
+    <t>0.9073,0.0346,0.0777,0.0068</t>
+  </si>
+  <si>
+    <t>0.9222,0.0777,0.0008,0.0023</t>
+  </si>
+  <si>
+    <t>0.9909,0.0023,0.0021,0.0019</t>
+  </si>
+  <si>
+    <t>0.9864,0.0070,0.0046,0.0011</t>
+  </si>
+  <si>
+    <t>0.9379,0.0745,0.0017,0.0020</t>
+  </si>
+  <si>
+    <t>0.0033,0.0173,0.9957,0.0005</t>
+  </si>
+  <si>
+    <t>0.9645,0.0307,0.0064,0.0008</t>
+  </si>
+  <si>
+    <t>0.0060,0.0180,0.9872,0.0091</t>
+  </si>
+  <si>
+    <t>0.0170,0.4068,0.9555,0.0083</t>
+  </si>
+  <si>
+    <t>0.0016,0.0021,0.9893,0.0167</t>
+  </si>
+  <si>
+    <t>0.0153,0.0484,0.9628,0.0044</t>
+  </si>
+  <si>
+    <t>0.1095,0.0033,0.9517,0.0002</t>
+  </si>
+  <si>
+    <t>0.0021,0.0002,0.9957,0.0014</t>
+  </si>
+  <si>
+    <t>0.0023,0.0213,0.9922,0.0035</t>
+  </si>
+  <si>
+    <t>0.1026,0.0088,0.9219,0.0024</t>
+  </si>
+  <si>
+    <t>0.1587,0.0030,0.9183,0.0009</t>
+  </si>
+  <si>
+    <t>0.0823,0.0049,0.9278,0.0016</t>
+  </si>
+  <si>
+    <t>0.0921,0.0604,0.8543,0.0077</t>
+  </si>
+  <si>
+    <t>0.0704,0.0145,0.9343,0.0014</t>
+  </si>
+  <si>
+    <t>0.8774,0.0549,0.0355,0.0017</t>
+  </si>
+  <si>
+    <t>0.8657,0.0197,0.0631,0.0210</t>
+  </si>
+  <si>
+    <t>0.4568,0.0087,0.5817,0.0021</t>
+  </si>
+  <si>
+    <t>0.0352,0.9698,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.0183,0.9788,0.0056,0.0010</t>
+  </si>
+  <si>
+    <t>0.4408,0.6968,0.0032,0.0002</t>
+  </si>
+  <si>
+    <t>0.9659,0.0404,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.9623,0.0329,0.0018,0.0026</t>
+  </si>
+  <si>
+    <t>0.8327,0.0097,0.2164,0.0009</t>
+  </si>
+  <si>
+    <t>0.9960,0.0006,0.0028,0.0001</t>
+  </si>
+  <si>
+    <t>0.8987,0.0051,0.0702,0.0169</t>
+  </si>
+  <si>
+    <t>0.6373,0.0056,0.4824,0.0075</t>
+  </si>
+  <si>
+    <t>0.8830,0.0011,0.0916,0.0066</t>
+  </si>
+  <si>
+    <t>0.0016,0.0020,0.9895,0.0317</t>
+  </si>
+  <si>
+    <t>0.0172,0.0371,0.9251,0.0360</t>
+  </si>
+  <si>
+    <t>0.3341,0.0026,0.8007,0.0009</t>
+  </si>
+  <si>
+    <t>0.6116,0.0345,0.3625,0.0078</t>
+  </si>
+  <si>
+    <t>0.0136,0.2113,0.9392,0.0023</t>
+  </si>
+  <si>
+    <t>0.9972,0.0004,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9923,0.0031,0.0006,0.0016</t>
+  </si>
+  <si>
+    <t>0.9832,0.0085,0.0040,0.0032</t>
+  </si>
+  <si>
+    <t>0.9708,0.0545,0.0020,0.0006</t>
+  </si>
+  <si>
+    <t>0.9943,0.0020,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9865,0.0104,0.0018,0.0010</t>
+  </si>
+  <si>
+    <t>0.9950,0.0007,0.0010,0.0014</t>
+  </si>
+  <si>
+    <t>0.9935,0.0022,0.0012,0.0013</t>
+  </si>
+  <si>
+    <t>0.0189,0.0421,0.9662,0.0059</t>
+  </si>
+  <si>
+    <t>0.0752,0.1202,0.8691,0.0080</t>
+  </si>
+  <si>
+    <t>0.9362,0.0026,0.0700,0.0023</t>
+  </si>
+  <si>
+    <t>0.0075,0.0022,0.9902,0.0007</t>
+  </si>
+  <si>
+    <t>0.0019,0.0067,0.9903,0.0032</t>
+  </si>
+  <si>
+    <t>0.0010,0.1923,0.9817,0.0020</t>
+  </si>
+  <si>
+    <t>0.0014,0.0025,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0911,0.0217,0.9070,0.0014</t>
+  </si>
+  <si>
+    <t>0.0004,0.0070,0.9986,0.0003</t>
+  </si>
+  <si>
+    <t>0.0038,0.0057,0.9892,0.0048</t>
+  </si>
+  <si>
+    <t>0.0232,0.0212,0.9556,0.0047</t>
+  </si>
+  <si>
+    <t>0.8236,0.0122,0.1900,0.0306</t>
+  </si>
+  <si>
+    <t>0.9285,0.0031,0.0697,0.0100</t>
+  </si>
+  <si>
+    <t>0.9858,0.0024,0.0117,0.0003</t>
+  </si>
+  <si>
+    <t>0.9931,0.0030,0.0011,0.0010</t>
+  </si>
+  <si>
+    <t>0.9962,0.0030,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9913,0.0071,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.9926,0.0039,0.0020,0.0006</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9876,0.0124,0.0021,0.0006</t>
+  </si>
+  <si>
+    <t>0.9650,0.0267,0.0044,0.0038</t>
+  </si>
+  <si>
+    <t>0.9965,0.0008,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.1141,0.2193,0.6381,0.0415</t>
+  </si>
+  <si>
+    <t>0.0063,0.2187,0.9860,0.0007</t>
+  </si>
+  <si>
+    <t>0.0009,0.0061,0.9965,0.0009</t>
+  </si>
+  <si>
+    <t>0.0200,0.0327,0.9356,0.0060</t>
+  </si>
+  <si>
+    <t>0.0034,0.0008,0.9967,0.0001</t>
+  </si>
+  <si>
+    <t>0.0693,0.0060,0.8889,0.0360</t>
+  </si>
+  <si>
+    <t>0.1219,0.0214,0.9037,0.0056</t>
+  </si>
+  <si>
+    <t>0.1850,0.0084,0.7993,0.0330</t>
+  </si>
+  <si>
+    <t>0.9831,0.0001,0.0007,0.0232</t>
+  </si>
+  <si>
+    <t>0.0595,0.0054,0.0049,0.9717</t>
+  </si>
+  <si>
+    <t>0.0545,0.0029,0.0016,0.9837</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.0004,0.9995</t>
+  </si>
+  <si>
+    <t>0.0094,0.0001,0.0003,0.9959</t>
+  </si>
+  <si>
+    <t>0.9818,0.0026,0.0004,0.0095</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,10 +2161,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2276,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2374,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2388,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2575,7 +2584,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2931,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,10 +2973,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,10 +2987,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,10 +3099,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3130,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3841,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3925,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4068,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4166,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4628,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4642,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4656,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4698,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4712,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4726,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4740,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4765,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4824,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,10 +4891,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
